--- a/data/eval/S1_post.xlsx
+++ b/data/eval/S1_post.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apoorva.ajay\Downloads\ApoorvaThesis\ApoorvaThesis\enrichment_api\data\eval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D657243C-10ED-4300-A0C9-51E3413E26A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568E843C-A2D3-4D39-AEE1-97AD004F6731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -4405,12 +4405,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4724,13 +4723,13 @@
     <col min="10" max="10" width="54.6640625" customWidth="1"/>
     <col min="23" max="23" width="21.33203125" customWidth="1"/>
     <col min="24" max="24" width="9" customWidth="1"/>
-    <col min="25" max="25" width="14.33203125" style="3" customWidth="1"/>
+    <col min="25" max="25" width="14.33203125" style="2" customWidth="1"/>
     <col min="26" max="26" width="30.77734375" customWidth="1"/>
     <col min="27" max="29" width="0" hidden="1" customWidth="1"/>
     <col min="30" max="30" width="12.88671875" customWidth="1"/>
     <col min="31" max="31" width="5.5546875" customWidth="1"/>
     <col min="32" max="32" width="11.109375" customWidth="1"/>
-    <col min="35" max="35" width="4.44140625" customWidth="1"/>
+    <col min="35" max="35" width="13" customWidth="1"/>
     <col min="36" max="36" width="4.109375" customWidth="1"/>
     <col min="37" max="37" width="16.109375" customWidth="1"/>
     <col min="38" max="38" width="13.109375" customWidth="1"/>
@@ -4809,7 +4808,7 @@
       <c r="X1" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z1" t="s">
@@ -5247,10 +5246,10 @@
       <c r="W4" t="s">
         <v>130</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="Y4" s="2" t="s">
         <v>1433</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="Z4" s="2" t="s">
         <v>131</v>
       </c>
       <c r="AH4" t="s">
@@ -6062,7 +6061,7 @@
       <c r="J11" t="s">
         <v>232</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="2" t="s">
         <v>233</v>
       </c>
       <c r="R11" t="s">
@@ -6074,7 +6073,7 @@
       <c r="X11" t="s">
         <v>235</v>
       </c>
-      <c r="Y11" s="3" t="s">
+      <c r="Y11" s="2" t="s">
         <v>1435</v>
       </c>
       <c r="AM11" t="s">
@@ -6312,7 +6311,7 @@
       <c r="W13" t="s">
         <v>254</v>
       </c>
-      <c r="Y13" s="3" t="s">
+      <c r="Y13" s="2" t="s">
         <v>1434</v>
       </c>
       <c r="Z13" t="s">
@@ -6565,7 +6564,7 @@
       <c r="W15" t="s">
         <v>254</v>
       </c>
-      <c r="Z15" s="3" t="s">
+      <c r="Z15" s="2" t="s">
         <v>280</v>
       </c>
       <c r="AM15" t="s">
@@ -10385,7 +10384,7 @@
       <c r="X47" t="s">
         <v>766</v>
       </c>
-      <c r="Y47" s="3" t="s">
+      <c r="Y47" s="2" t="s">
         <v>1440</v>
       </c>
       <c r="AF47" t="s">
@@ -12477,7 +12476,7 @@
       <c r="K64" t="s">
         <v>975</v>
       </c>
-      <c r="L64" s="3" t="s">
+      <c r="L64" s="2" t="s">
         <v>976</v>
       </c>
       <c r="R64" t="s">
@@ -12599,7 +12598,7 @@
       <c r="K65" t="s">
         <v>975</v>
       </c>
-      <c r="L65" s="3" t="s">
+      <c r="L65" s="2" t="s">
         <v>981</v>
       </c>
       <c r="R65" t="s">
@@ -12977,7 +12976,7 @@
       <c r="X68" t="s">
         <v>1003</v>
       </c>
-      <c r="Y68" s="3" t="s">
+      <c r="Y68" s="2" t="s">
         <v>1444</v>
       </c>
       <c r="Z68" t="s">
@@ -13230,7 +13229,7 @@
       <c r="K70" t="s">
         <v>763</v>
       </c>
-      <c r="L70" s="3" t="s">
+      <c r="L70" s="2" t="s">
         <v>1025</v>
       </c>
       <c r="R70" t="s">
